--- a/scraper/downloads/yad2_page_2.xlsx
+++ b/scraper/downloads/yad2_page_2.xlsx
@@ -333,26 +333,33 @@
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">בוסתנאי</t>
+          <t xml:space="preserve">ארלוזורוב</t>
         </is>
       </c>
       <c r="D3" s="65">
-        <v>16</v>
-      </c>
-      <c r="E3" s="65">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c t="inlineStr" r="E3">
+        <is>
+          <t xml:space="preserve">/53</t>
+        </is>
       </c>
       <c t="inlineStr" r="F3">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G3" s="65">
-        <v>0</v>
+      <c t="n" r="G3">
+        <v>2.5</v>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">150מ״ר</t>
+          <t xml:space="preserve">59מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I3">
+        <is>
+          <t xml:space="preserve">מרפסת: 12מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
@@ -362,16 +369,21 @@
       </c>
       <c t="inlineStr" r="K3">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L3">
+        <is>
+          <t xml:space="preserve">צפון מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N3">
         <is>
-          <t xml:space="preserve">בובליל מתווך לורן(052) 286-0799</t>
-        </is>
-      </c>
-      <c r="O3" s="65">
-        <v>0</v>
+          <t xml:space="preserve">ארז נתנאלי- לא לפנות(054) 743-3889שוכרת- ניצן(054) 492-2952</t>
+        </is>
+      </c>
+      <c r="O3" s="63">
+        <v>5490000</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -380,7 +392,7 @@
       </c>
       <c t="inlineStr" r="S3">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">אורן כהן06-01-2025</t>
         </is>
       </c>
     </row>
@@ -395,18 +407,18 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">בלומנפלד</t>
+          <t xml:space="preserve">בוסתנאי</t>
         </is>
       </c>
       <c r="D4" s="65">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E4" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G4" s="65">
@@ -414,12 +426,7 @@
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">600מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I4">
-        <is>
-          <t xml:space="preserve">מרתף: 400מ״ר</t>
+          <t xml:space="preserve">150מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
@@ -432,18 +439,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L4">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t xml:space="preserve">יובל/ג'רארד(050) 731-3496</t>
-        </is>
-      </c>
-      <c r="O4" s="63">
-        <v>12800000</v>
+          <t xml:space="preserve">בובליל מתווך לורן(052) 286-0799</t>
+        </is>
+      </c>
+      <c r="O4" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -452,7 +454,7 @@
       </c>
       <c t="inlineStr" r="S4">
         <is>
-          <t xml:space="preserve">מיכאל בלוך18-11-2025</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -467,36 +469,36 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">בלפור</t>
+          <t xml:space="preserve">בלומנפלד</t>
         </is>
       </c>
       <c r="D5" s="65">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E5" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="n" r="G5">
-        <v>5.5</v>
+          <t xml:space="preserve">בית פרטי</t>
+        </is>
+      </c>
+      <c r="G5" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">282מ״ר</t>
+          <t xml:space="preserve">600מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t xml:space="preserve">מרפסת: 11מ״ר</t>
+          <t xml:space="preserve">מרתף: 400מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K5">
@@ -511,11 +513,11 @@
       </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t xml:space="preserve">גואטה</t>
+          <t xml:space="preserve">יובל/ג'רארד(050) 731-3496</t>
         </is>
       </c>
       <c r="O5" s="63">
-        <v>22000000</v>
+        <v>12800000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -524,7 +526,7 @@
       </c>
       <c t="inlineStr" r="S5">
         <is>
-          <t xml:space="preserve">אורן כהן26-08-2024</t>
+          <t xml:space="preserve">מיכאל בלוך18-11-2025</t>
         </is>
       </c>
     </row>
@@ -543,12 +545,10 @@
         </is>
       </c>
       <c r="D6" s="65">
-        <v>5</v>
-      </c>
-      <c t="inlineStr" r="E6">
-        <is>
-          <t xml:space="preserve">/31</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="E6" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F6">
         <is>
@@ -556,16 +556,21 @@
         </is>
       </c>
       <c t="n" r="G6">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">68מ״ר</t>
+          <t xml:space="preserve">282מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I6">
+        <is>
+          <t xml:space="preserve">מרפסת: 11מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K6">
@@ -573,13 +578,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L6">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t xml:space="preserve">רבקה(050) 200-3333</t>
+          <t xml:space="preserve">גואטה</t>
         </is>
       </c>
       <c r="O6" s="63">
-        <v>10000</v>
+        <v>22000000</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -588,7 +598,7 @@
       </c>
       <c t="inlineStr" r="S6">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות09-06-2024</t>
+          <t xml:space="preserve">אורן כהן26-08-2024</t>
         </is>
       </c>
     </row>
@@ -603,15 +613,15 @@
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">בן לברט</t>
+          <t xml:space="preserve">בלפור</t>
         </is>
       </c>
       <c r="D7" s="65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">/33</t>
+          <t xml:space="preserve">/31</t>
         </is>
       </c>
       <c t="inlineStr" r="F7">
@@ -620,35 +630,30 @@
         </is>
       </c>
       <c t="n" r="G7">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">100מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I7">
-        <is>
-          <t xml:space="preserve">מרפסת: 2מ״ר</t>
+          <t xml:space="preserve">68מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K7">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t xml:space="preserve">תמיר לוקשיין נכסים (מתווך)(050) 307-0033</t>
+          <t xml:space="preserve">רבקה(050) 200-3333</t>
         </is>
       </c>
       <c r="O7" s="63">
-        <v>4750000</v>
+        <v>10000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -657,7 +662,7 @@
       </c>
       <c t="inlineStr" r="S7">
         <is>
-          <t xml:space="preserve">מנחם אוריאל18-01-2026</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות09-06-2024</t>
         </is>
       </c>
     </row>
@@ -672,15 +677,15 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">בן מיימון</t>
+          <t xml:space="preserve">בן לברט</t>
         </is>
       </c>
       <c r="D8" s="65">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">/42</t>
+          <t xml:space="preserve">/33</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
@@ -688,36 +693,36 @@
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G8" s="65">
-        <v>5</v>
+      <c t="n" r="G8">
+        <v>4.5</v>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">150מ״ר</t>
+          <t xml:space="preserve">100מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
         <is>
-          <t xml:space="preserve">מרפסת: 20מ״ר</t>
+          <t xml:space="preserve">מרפסת: 2מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K8">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N8">
         <is>
-          <t xml:space="preserve">סיון מתווך(054) 263-7427</t>
+          <t xml:space="preserve">תמיר לוקשיין נכסים (מתווך)(050) 307-0033</t>
         </is>
       </c>
       <c r="O8" s="63">
-        <v>11500000</v>
+        <v>4750000</v>
       </c>
       <c t="inlineStr" r="R8">
         <is>
@@ -726,7 +731,7 @@
       </c>
       <c t="inlineStr" r="S8">
         <is>
-          <t xml:space="preserve">מנחם אוריאל15-01-2026</t>
+          <t xml:space="preserve">מנחם אוריאל18-01-2026</t>
         </is>
       </c>
     </row>
@@ -741,62 +746,52 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">בן מימון</t>
+          <t xml:space="preserve">בן מיימון</t>
         </is>
       </c>
       <c r="D9" s="65">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">/55</t>
+          <t xml:space="preserve">/42</t>
         </is>
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G9" s="65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">388מ״ר</t>
+          <t xml:space="preserve">150מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
         <is>
-          <t xml:space="preserve">מרפסת: 182מ״ר</t>
+          <t xml:space="preserve">מרפסת: 20מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K9">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L9">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M9">
-        <is>
-          <t xml:space="preserve">חזית עורף</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N9">
         <is>
-          <t xml:space="preserve">קפיטל</t>
-        </is>
-      </c>
-      <c r="O9" s="65">
-        <v>0</v>
+          <t xml:space="preserve">סיון מתווך(054) 263-7427</t>
+        </is>
+      </c>
+      <c r="O9" s="63">
+        <v>11500000</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -805,7 +800,7 @@
       </c>
       <c t="inlineStr" r="S9">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">מנחם אוריאל15-01-2026</t>
         </is>
       </c>
     </row>
@@ -820,47 +815,62 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">בפלמ"ח</t>
+          <t xml:space="preserve">בן מימון</t>
         </is>
       </c>
       <c r="D10" s="65">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">/33</t>
+          <t xml:space="preserve">/55</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G10" s="65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">77מ״ר</t>
+          <t xml:space="preserve">388מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I10">
+        <is>
+          <t xml:space="preserve">מרפסת: 182מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K10">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L10">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M10">
+        <is>
+          <t xml:space="preserve">חזית עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N10">
         <is>
-          <t xml:space="preserve">מירב - מתווכת רימקס+972 54-725-3365</t>
-        </is>
-      </c>
-      <c r="O10" s="63">
-        <v>3270000</v>
+          <t xml:space="preserve">קפיטל</t>
+        </is>
+      </c>
+      <c r="O10" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -869,7 +879,7 @@
       </c>
       <c t="inlineStr" r="S10">
         <is>
-          <t xml:space="preserve">מנחם אוריאל16-02-2026</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -884,26 +894,28 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">ברכיהו</t>
+          <t xml:space="preserve">בפלמ"ח</t>
         </is>
       </c>
       <c r="D11" s="65">
+        <v>60</v>
+      </c>
+      <c t="inlineStr" r="E11">
+        <is>
+          <t xml:space="preserve">/33</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F11">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c r="G11" s="65">
         <v>3</v>
       </c>
-      <c r="E11" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="F11">
-        <is>
-          <t xml:space="preserve">בית פרטי</t>
-        </is>
-      </c>
-      <c r="G11" s="65">
-        <v>0</v>
-      </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">1500מ״ר</t>
+          <t xml:space="preserve">77מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
@@ -916,18 +928,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L11">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N11">
         <is>
-          <t xml:space="preserve">אודי קראוס(052) 260-1193</t>
+          <t xml:space="preserve">מירב - מתווכת רימקס+972 54-725-3365</t>
         </is>
       </c>
       <c r="O11" s="63">
-        <v>120000000</v>
+        <v>3270000</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -936,7 +943,7 @@
       </c>
       <c t="inlineStr" r="S11">
         <is>
-          <t xml:space="preserve">אורן כהן08-06-2026</t>
+          <t xml:space="preserve">מנחם אוריאל16-02-2026</t>
         </is>
       </c>
     </row>
@@ -951,18 +958,18 @@
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">ברנר</t>
+          <t xml:space="preserve">ברכיהו</t>
         </is>
       </c>
       <c r="D12" s="65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G12" s="65">
@@ -970,7 +977,7 @@
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">125מ״ר</t>
+          <t xml:space="preserve">1500מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
@@ -983,8 +990,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L12">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N12">
+        <is>
+          <t xml:space="preserve">אודי קראוס(052) 260-1193</t>
+        </is>
+      </c>
       <c r="O12" s="63">
-        <v>8500</v>
+        <v>120000000</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -993,7 +1010,7 @@
       </c>
       <c t="inlineStr" r="S12">
         <is>
-          <t xml:space="preserve">מירי רענן28-10-2024</t>
+          <t xml:space="preserve">אורן כהן08-06-2026</t>
         </is>
       </c>
     </row>
@@ -1008,31 +1025,26 @@
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">גבע</t>
+          <t xml:space="preserve">ברנר</t>
         </is>
       </c>
       <c r="D13" s="65">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E13" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G13" s="65">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">240מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I13">
-        <is>
-          <t xml:space="preserve">מרפסת: 20מ״רגינה: 20מ״ר</t>
+          <t xml:space="preserve">125מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
@@ -1045,18 +1057,8 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L13">
-        <is>
-          <t xml:space="preserve">דרום מזרח מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N13">
-        <is>
-          <t xml:space="preserve">Joey Harari(054) 225-5724</t>
-        </is>
-      </c>
       <c r="O13" s="63">
-        <v>12708000</v>
+        <v>8500</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -1065,7 +1067,7 @@
       </c>
       <c t="inlineStr" r="S13">
         <is>
-          <t xml:space="preserve">אריה טאו31-12-2025</t>
+          <t xml:space="preserve">מירי רענן28-10-2024</t>
         </is>
       </c>
     </row>
@@ -1080,50 +1082,55 @@
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">גבעות עדן</t>
+          <t xml:space="preserve">גבע</t>
         </is>
       </c>
       <c r="D14" s="65">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="E14" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">דו משפחתי</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G14" s="65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">156מ״ר</t>
+          <t xml:space="preserve">240מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t xml:space="preserve">גינה: 114מ״ר</t>
+          <t xml:space="preserve">מרפסת: 20מ״רגינה: 20מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K14">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L14">
+        <is>
+          <t xml:space="preserve">דרום מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t xml:space="preserve">ידידיה נוה(053) 421-4454</t>
+          <t xml:space="preserve">Joey Harari(054) 225-5724</t>
         </is>
       </c>
       <c r="O14" s="63">
-        <v>5200000</v>
+        <v>12708000</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -1132,7 +1139,7 @@
       </c>
       <c t="inlineStr" r="S14">
         <is>
-          <t xml:space="preserve">אריה טאו27-08-2025</t>
+          <t xml:space="preserve">אריה טאו31-12-2025</t>
         </is>
       </c>
     </row>
@@ -1147,45 +1154,50 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">גד</t>
+          <t xml:space="preserve">גבעות עדן</t>
         </is>
       </c>
       <c r="D15" s="65">
+        <v>106</v>
+      </c>
+      <c r="E15" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="F15">
+        <is>
+          <t xml:space="preserve">דו משפחתי</t>
+        </is>
+      </c>
+      <c r="G15" s="65">
         <v>6</v>
       </c>
-      <c r="E15" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="F15">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c r="G15" s="65">
-        <v>8</v>
-      </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">344מ״ר</t>
+          <t xml:space="preserve">156מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I15">
+        <is>
+          <t xml:space="preserve">גינה: 114מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K15">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t xml:space="preserve">רוגוף נתניאל16466759875</t>
-        </is>
-      </c>
-      <c r="O15" s="65">
-        <v>0</v>
+          <t xml:space="preserve">ידידיה נוה(053) 421-4454</t>
+        </is>
+      </c>
+      <c r="O15" s="63">
+        <v>5200000</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -1194,7 +1206,7 @@
       </c>
       <c t="inlineStr" r="S15">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">אריה טאו27-08-2025</t>
         </is>
       </c>
     </row>
@@ -1209,28 +1221,26 @@
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">גדעון</t>
+          <t xml:space="preserve">גד</t>
         </is>
       </c>
       <c r="D16" s="65">
-        <v>19</v>
-      </c>
-      <c t="inlineStr" r="E16">
-        <is>
-          <t xml:space="preserve">/10</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E16" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G16" s="65">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">72מ״ר</t>
+          <t xml:space="preserve">344מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
@@ -1245,11 +1255,11 @@
       </c>
       <c t="inlineStr" r="N16">
         <is>
-          <t xml:space="preserve">אפרת שבח(050) 965-0690</t>
-        </is>
-      </c>
-      <c r="O16" s="63">
-        <v>5500000</v>
+          <t xml:space="preserve">רוגוף נתניאל16466759875</t>
+        </is>
+      </c>
+      <c r="O16" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R16">
         <is>
@@ -1258,7 +1268,7 @@
       </c>
       <c t="inlineStr" r="S16">
         <is>
-          <t xml:space="preserve">מירי רענן24-02-2025</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1281,20 +1291,20 @@
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">/11</t>
+          <t xml:space="preserve">/10</t>
         </is>
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="n" r="G17">
-        <v>3.5</v>
+          <t xml:space="preserve">דירת גן</t>
+        </is>
+      </c>
+      <c r="G17" s="65">
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">84מ״ר</t>
+          <t xml:space="preserve">72מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
@@ -1307,18 +1317,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L17">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N17">
         <is>
-          <t xml:space="preserve">אפרת שבח</t>
+          <t xml:space="preserve">אפרת שבח(050) 965-0690</t>
         </is>
       </c>
       <c r="O17" s="63">
-        <v>6490000</v>
+        <v>5500000</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1342,15 +1347,15 @@
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">גרץ</t>
+          <t xml:space="preserve">גדעון</t>
         </is>
       </c>
       <c r="D18" s="65">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">/64</t>
+          <t xml:space="preserve">/11</t>
         </is>
       </c>
       <c t="inlineStr" r="F18">
@@ -1358,12 +1363,12 @@
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G18" s="65">
-        <v>5</v>
+      <c t="n" r="G18">
+        <v>3.5</v>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">170מ״ר</t>
+          <t xml:space="preserve">84מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
@@ -1378,21 +1383,16 @@
       </c>
       <c t="inlineStr" r="L18">
         <is>
-          <t xml:space="preserve">מזרח מערב</t>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N18">
         <is>
-          <t xml:space="preserve">יצחק קוולסקי (מתווך)054-7660338</t>
+          <t xml:space="preserve">אפרת שבח</t>
         </is>
       </c>
       <c r="O18" s="63">
-        <v>9800000</v>
-      </c>
-      <c t="inlineStr" r="P18">
-        <is>
-          <t xml:space="preserve">מעלית</t>
-        </is>
+        <v>6490000</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1401,7 +1401,7 @@
       </c>
       <c t="inlineStr" r="S18">
         <is>
-          <t xml:space="preserve">מנחם אוריאל11-02-2026</t>
+          <t xml:space="preserve">מירי רענן24-02-2025</t>
         </is>
       </c>
     </row>
@@ -1420,11 +1420,11 @@
         </is>
       </c>
       <c r="D19" s="65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">/55</t>
+          <t xml:space="preserve">/64</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="G19" s="65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">157מ״ר</t>
+          <t xml:space="preserve">170מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K19">
@@ -1450,13 +1450,23 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L19">
+        <is>
+          <t xml:space="preserve">מזרח מערב</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t xml:space="preserve">אניטה ויצמן - מתווכת054-5821210</t>
+          <t xml:space="preserve">יצחק קוולסקי (מתווך)054-7660338</t>
         </is>
       </c>
       <c r="O19" s="63">
-        <v>10000000</v>
+        <v>9800000</v>
+      </c>
+      <c t="inlineStr" r="P19">
+        <is>
+          <t xml:space="preserve">מעלית</t>
+        </is>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1465,7 +1475,7 @@
       </c>
       <c t="inlineStr" r="S19">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות15-02-2026</t>
+          <t xml:space="preserve">מנחם אוריאל11-02-2026</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1490,11 @@
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">גרשון אבנר</t>
+          <t xml:space="preserve">גרץ</t>
         </is>
       </c>
       <c r="D20" s="65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c t="inlineStr" r="E20">
         <is>
@@ -1493,39 +1503,34 @@
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">מ.פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G20" s="65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">130מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I20">
-        <is>
-          <t xml:space="preserve">מרפסת: 50מ״ר</t>
+          <t xml:space="preserve">157מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K20">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L20">
-        <is>
-          <t xml:space="preserve">דרום מזרח מערב</t>
+          <t xml:space="preserve">ללא מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N20">
+        <is>
+          <t xml:space="preserve">אניטה ויצמן - מתווכת054-5821210</t>
         </is>
       </c>
       <c r="O20" s="63">
-        <v>4550000</v>
+        <v>10000000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1534,7 +1539,7 @@
       </c>
       <c t="inlineStr" r="S20">
         <is>
-          <t xml:space="preserve">אריה טאו10-07-2025</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות15-02-2026</t>
         </is>
       </c>
     </row>
@@ -1549,50 +1554,52 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">דוד מרכוס</t>
+          <t xml:space="preserve">גרשון אבנר</t>
         </is>
       </c>
       <c r="D21" s="65">
-        <v>14</v>
-      </c>
-      <c r="E21" s="65">
         <v>5</v>
       </c>
+      <c t="inlineStr" r="E21">
+        <is>
+          <t xml:space="preserve">/55</t>
+        </is>
+      </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">מ.פנטהאוז</t>
         </is>
       </c>
       <c r="G21" s="65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">201מ״ר</t>
+          <t xml:space="preserve">130מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t xml:space="preserve">מרפסת: 17מ״ר</t>
+          <t xml:space="preserve">מרפסת: 50מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K21">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N21">
-        <is>
-          <t xml:space="preserve">שבסון(050) 903-2013</t>
-        </is>
-      </c>
-      <c r="O21" s="65">
-        <v>0</v>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L21">
+        <is>
+          <t xml:space="preserve">דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c r="O21" s="63">
+        <v>4550000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1601,7 +1608,7 @@
       </c>
       <c t="inlineStr" r="S21">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">אריה טאו10-07-2025</t>
         </is>
       </c>
     </row>
@@ -1616,26 +1623,31 @@
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">דיסקין</t>
+          <t xml:space="preserve">דוד מרכוס</t>
         </is>
       </c>
       <c r="D22" s="65">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" s="65">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G22" s="65">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">302מ״ר</t>
+          <t xml:space="preserve">201מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I22">
+        <is>
+          <t xml:space="preserve">מרפסת: 17מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
@@ -1650,7 +1662,7 @@
       </c>
       <c t="inlineStr" r="N22">
         <is>
-          <t xml:space="preserve">יהב יגאל(847) 722-8787</t>
+          <t xml:space="preserve">שבסון(050) 903-2013</t>
         </is>
       </c>
       <c r="O22" s="65">
@@ -1663,7 +1675,7 @@
       </c>
       <c t="inlineStr" r="S22">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1682,27 +1694,22 @@
         </is>
       </c>
       <c r="D23" s="65">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E23" s="65">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G23" s="65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">550מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I23">
-        <is>
-          <t xml:space="preserve">מרפסת: 260מ״ר</t>
+          <t xml:space="preserve">302מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
@@ -1715,18 +1722,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L23">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N23">
         <is>
-          <t xml:space="preserve">שמואל דנזל(054) 900-0340</t>
-        </is>
-      </c>
-      <c r="O23" s="63">
-        <v>38000000</v>
+          <t xml:space="preserve">יהב יגאל(847) 722-8787</t>
+        </is>
+      </c>
+      <c r="O23" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R23">
         <is>
@@ -1735,7 +1737,7 @@
       </c>
       <c t="inlineStr" r="S23">
         <is>
-          <t xml:space="preserve">אורן כהן28-09-2025</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1750,18 +1752,18 @@
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">החי"ם</t>
+          <t xml:space="preserve">דיסקין</t>
         </is>
       </c>
       <c r="D24" s="65">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E24" s="65">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G24" s="65">
@@ -1769,12 +1771,12 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">200מ״ר</t>
+          <t xml:space="preserve">550מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">גינה: 500מ״ר</t>
+          <t xml:space="preserve">מרפסת: 260מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
@@ -1787,13 +1789,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L24">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N24">
         <is>
-          <t xml:space="preserve">רב מאיר ארביבו(054) 841-6163</t>
+          <t xml:space="preserve">שמואל דנזל(054) 900-0340</t>
         </is>
       </c>
       <c r="O24" s="63">
-        <v>40000000</v>
+        <v>38000000</v>
       </c>
       <c t="inlineStr" r="R24">
         <is>
@@ -1802,7 +1809,7 @@
       </c>
       <c t="inlineStr" r="S24">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות26-10-2025</t>
+          <t xml:space="preserve">אורן כהן28-09-2025</t>
         </is>
       </c>
     </row>
@@ -1817,31 +1824,31 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">הנביאים</t>
+          <t xml:space="preserve">החי"ם</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E25" s="65">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">דופלקס</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G25" s="65">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">282מ״ר</t>
+          <t xml:space="preserve">200מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">מרפסת: 131מ״ר</t>
+          <t xml:space="preserve">גינה: 500מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
@@ -1856,11 +1863,11 @@
       </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t xml:space="preserve">שמואל אליהו(054) 667-0500</t>
+          <t xml:space="preserve">רב מאיר ארביבו(054) 841-6163</t>
         </is>
       </c>
       <c r="O25" s="63">
-        <v>29000000</v>
+        <v>40000000</v>
       </c>
       <c t="inlineStr" r="R25">
         <is>
@@ -1869,7 +1876,7 @@
       </c>
       <c t="inlineStr" r="S25">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות26-10-2025</t>
         </is>
       </c>
     </row>
@@ -1888,27 +1895,27 @@
         </is>
       </c>
       <c r="D26" s="65">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E26" s="65">
+        <v>8</v>
+      </c>
+      <c t="inlineStr" r="F26">
+        <is>
+          <t xml:space="preserve">דופלקס</t>
+        </is>
+      </c>
+      <c r="G26" s="65">
         <v>6</v>
       </c>
-      <c t="inlineStr" r="F26">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c r="G26" s="65">
-        <v>5</v>
-      </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">139.5מ״ר</t>
+          <t xml:space="preserve">282מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t xml:space="preserve">מרפסת: 4.1מ״ר</t>
+          <t xml:space="preserve">מרפסת: 131מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
@@ -1923,11 +1930,11 @@
       </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t xml:space="preserve">בר חיים גלעד</t>
-        </is>
-      </c>
-      <c r="O26" s="65">
-        <v>0</v>
+          <t xml:space="preserve">שמואל אליהו(054) 667-0500</t>
+        </is>
+      </c>
+      <c r="O26" s="63">
+        <v>29000000</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1958,11 +1965,11 @@
         <v>45</v>
       </c>
       <c r="E27" s="65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">דופלקס</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G27" s="65">
@@ -1970,12 +1977,12 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">185מ״ר</t>
+          <t xml:space="preserve">139.5מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t xml:space="preserve">מרפסת: 44מ״ר</t>
+          <t xml:space="preserve">מרפסת: 4.1מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
@@ -1990,7 +1997,7 @@
       </c>
       <c t="inlineStr" r="N27">
         <is>
-          <t xml:space="preserve">ברגר נפתלי19177515365</t>
+          <t xml:space="preserve">בר חיים גלעד</t>
         </is>
       </c>
       <c r="O27" s="65">
